--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/174.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/174.xlsx
@@ -426,13 +426,13 @@
         <v>-15.32436703375136</v>
       </c>
       <c r="E2">
-        <v>-6.082797803452679</v>
+        <v>-7.217284697276281</v>
       </c>
       <c r="F2">
-        <v>-5.953570276684071</v>
+        <v>-4.70755659674111</v>
       </c>
       <c r="G2">
-        <v>-1.143996577764425</v>
+        <v>-3.937974522724353</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.22953083003535</v>
       </c>
       <c r="E3">
-        <v>-6.575835411037789</v>
+        <v>-7.66054079009507</v>
       </c>
       <c r="F3">
-        <v>-5.063026444997837</v>
+        <v>-4.85841969650636</v>
       </c>
       <c r="G3">
-        <v>-1.988374391374316</v>
+        <v>-4.206254512135811</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.95506742251257</v>
       </c>
       <c r="E4">
-        <v>-5.913179281021378</v>
+        <v>-8.366960092921607</v>
       </c>
       <c r="F4">
-        <v>-5.162600348651352</v>
+        <v>-4.671515159412707</v>
       </c>
       <c r="G4">
-        <v>-1.88283751012789</v>
+        <v>-3.792012569897887</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.52604566199581</v>
       </c>
       <c r="E5">
-        <v>-8.492742986958659</v>
+        <v>-9.472614192738371</v>
       </c>
       <c r="F5">
-        <v>-5.047466391703652</v>
+        <v>-4.271420330799768</v>
       </c>
       <c r="G5">
-        <v>-1.885942801843726</v>
+        <v>-2.678096759571614</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.97322759713661</v>
       </c>
       <c r="E6">
-        <v>-10.41653384337119</v>
+        <v>-10.29759800203373</v>
       </c>
       <c r="F6">
-        <v>-5.488816402078214</v>
+        <v>-4.463539440694044</v>
       </c>
       <c r="G6">
-        <v>-1.416179700366684</v>
+        <v>-4.13867303549713</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.31108751922641</v>
       </c>
       <c r="E7">
-        <v>-8.891710603982434</v>
+        <v>-11.56406727081089</v>
       </c>
       <c r="F7">
-        <v>-5.339431109759559</v>
+        <v>-4.747213857782734</v>
       </c>
       <c r="G7">
-        <v>-1.855316945059928</v>
+        <v>-4.224230774414054</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.57699109772371</v>
       </c>
       <c r="E8">
-        <v>-11.33387588005299</v>
+        <v>-12.26405614054653</v>
       </c>
       <c r="F8">
-        <v>-4.795245913266661</v>
+        <v>-4.536099454974863</v>
       </c>
       <c r="G8">
-        <v>-1.317638001844738</v>
+        <v>-4.129350539258542</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.80091257168457</v>
       </c>
       <c r="E9">
-        <v>-12.91720247514684</v>
+        <v>-12.75637824923843</v>
       </c>
       <c r="F9">
-        <v>-5.549027115118099</v>
+        <v>-4.552885492025193</v>
       </c>
       <c r="G9">
-        <v>-1.472091503979435</v>
+        <v>-3.340477332160072</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.9932914009592</v>
       </c>
       <c r="E10">
-        <v>-13.05456920569551</v>
+        <v>-14.09203354390477</v>
       </c>
       <c r="F10">
-        <v>-4.984268585809271</v>
+        <v>-4.539540493166093</v>
       </c>
       <c r="G10">
-        <v>-1.061170038917399</v>
+        <v>-2.388973575444904</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.19428561757824</v>
       </c>
       <c r="E11">
-        <v>-14.40012827301662</v>
+        <v>-16.56535924962211</v>
       </c>
       <c r="F11">
-        <v>-5.326761230333741</v>
+        <v>-4.63175932265015</v>
       </c>
       <c r="G11">
-        <v>-0.5010787024013422</v>
+        <v>-2.902485536223415</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.427731088743107</v>
       </c>
       <c r="E12">
-        <v>-14.53069776407978</v>
+        <v>-15.28771370699402</v>
       </c>
       <c r="F12">
-        <v>-4.692954136164561</v>
+        <v>-4.454982405423125</v>
       </c>
       <c r="G12">
-        <v>0.1377274754019653</v>
+        <v>-2.136329292615424</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.705889016565541</v>
       </c>
       <c r="E13">
-        <v>-14.63711690326004</v>
+        <v>-16.8346313710662</v>
       </c>
       <c r="F13">
-        <v>-4.532309674107055</v>
+        <v>-4.34740730102597</v>
       </c>
       <c r="G13">
-        <v>-0.130453197643315</v>
+        <v>-1.514824025800347</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.068514616231539</v>
       </c>
       <c r="E14">
-        <v>-17.1532638591939</v>
+        <v>-17.66136769980253</v>
       </c>
       <c r="F14">
-        <v>-4.951443699105938</v>
+        <v>-4.500474686450068</v>
       </c>
       <c r="G14">
-        <v>0.3730807788798325</v>
+        <v>-0.6919217211037083</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.52514980299438</v>
       </c>
       <c r="E15">
-        <v>-18.902047309106</v>
+        <v>-19.28590793684019</v>
       </c>
       <c r="F15">
-        <v>-4.834859270835936</v>
+        <v>-4.520415146570257</v>
       </c>
       <c r="G15">
-        <v>0.4971600256917166</v>
+        <v>0.3119052078596403</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.079913319640998</v>
       </c>
       <c r="E16">
-        <v>-19.79559221487749</v>
+        <v>-20.00479865708385</v>
       </c>
       <c r="F16">
-        <v>-4.698423846125246</v>
+        <v>-4.124952548473773</v>
       </c>
       <c r="G16">
-        <v>2.735985968080182</v>
+        <v>0.3154938392242102</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.744550322007844</v>
       </c>
       <c r="E17">
-        <v>-18.80012947308937</v>
+        <v>-21.10468800948885</v>
       </c>
       <c r="F17">
-        <v>-4.312725214605559</v>
+        <v>-3.743224281915705</v>
       </c>
       <c r="G17">
-        <v>3.43420319613125</v>
+        <v>0.886404038562605</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.499872292912479</v>
       </c>
       <c r="E18">
-        <v>-20.07811917974204</v>
+        <v>-21.54654933231328</v>
       </c>
       <c r="F18">
-        <v>-4.551659508269049</v>
+        <v>-3.726002523611504</v>
       </c>
       <c r="G18">
-        <v>3.434103879765072</v>
+        <v>1.270083024381979</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.332968349630461</v>
       </c>
       <c r="E19">
-        <v>-21.64358094487563</v>
+        <v>-23.03480061561609</v>
       </c>
       <c r="F19">
-        <v>-4.695180787743286</v>
+        <v>-3.784428104898355</v>
       </c>
       <c r="G19">
-        <v>3.798945861465992</v>
+        <v>2.375156367572858</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.233016342870244</v>
       </c>
       <c r="E20">
-        <v>-20.74609626671747</v>
+        <v>-23.36663813395015</v>
       </c>
       <c r="F20">
-        <v>-4.014113676509589</v>
+        <v>-3.2552578959486</v>
       </c>
       <c r="G20">
-        <v>4.415025144142203</v>
+        <v>2.538495373934959</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.170907594646326</v>
       </c>
       <c r="E21">
-        <v>-23.66579365537087</v>
+        <v>-23.94869648357805</v>
       </c>
       <c r="F21">
-        <v>-4.391715845034312</v>
+        <v>-3.346538185165286</v>
       </c>
       <c r="G21">
-        <v>3.82943598588268</v>
+        <v>2.862352801859702</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.138602616494111</v>
       </c>
       <c r="E22">
-        <v>-22.63445634249398</v>
+        <v>-25.04284373094132</v>
       </c>
       <c r="F22">
-        <v>-3.694303388208575</v>
+        <v>-3.165828179509769</v>
       </c>
       <c r="G22">
-        <v>4.40390833222133</v>
+        <v>2.681699642327213</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.125896969188512</v>
       </c>
       <c r="E23">
-        <v>-24.74838423706657</v>
+        <v>-25.85408815009741</v>
       </c>
       <c r="F23">
-        <v>-3.505853945908701</v>
+        <v>-3.009560810808656</v>
       </c>
       <c r="G23">
-        <v>4.490949195539848</v>
+        <v>3.887416880457475</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.113694880663905</v>
       </c>
       <c r="E24">
-        <v>-24.32287070540983</v>
+        <v>-25.74476625907824</v>
       </c>
       <c r="F24">
-        <v>-3.176966407607811</v>
+        <v>-2.708818711752684</v>
       </c>
       <c r="G24">
-        <v>4.112643225130712</v>
+        <v>3.466716063872432</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.106474190173491</v>
       </c>
       <c r="E25">
-        <v>-24.33465379477779</v>
+        <v>-25.89455459382996</v>
       </c>
       <c r="F25">
-        <v>-2.742633497502363</v>
+        <v>-2.920110385184754</v>
       </c>
       <c r="G25">
-        <v>3.493548035468225</v>
+        <v>3.425923521737532</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.101709901295392</v>
       </c>
       <c r="E26">
-        <v>-24.03809308896347</v>
+        <v>-26.39942963247112</v>
       </c>
       <c r="F26">
-        <v>-2.970470153070548</v>
+        <v>-3.043206609608164</v>
       </c>
       <c r="G26">
-        <v>4.073476160855595</v>
+        <v>3.691141256525165</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.092720635158691</v>
       </c>
       <c r="E27">
-        <v>-23.92960896563572</v>
+        <v>-26.11203908652233</v>
       </c>
       <c r="F27">
-        <v>-3.304777699287955</v>
+        <v>-3.018671195504645</v>
       </c>
       <c r="G27">
-        <v>4.140921905127167</v>
+        <v>3.538237089702847</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.093911682671732</v>
       </c>
       <c r="E28">
-        <v>-25.50046867178645</v>
+        <v>-26.32335126914225</v>
       </c>
       <c r="F28">
-        <v>-2.480668104938839</v>
+        <v>-2.592936739040256</v>
       </c>
       <c r="G28">
-        <v>2.841642028966021</v>
+        <v>3.043274115580872</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.106831667135268</v>
       </c>
       <c r="E29">
-        <v>-23.8330120865781</v>
+        <v>-26.1196922075953</v>
       </c>
       <c r="F29">
-        <v>-3.311661432405219</v>
+        <v>-2.737207691014026</v>
       </c>
       <c r="G29">
-        <v>4.613690981953867</v>
+        <v>2.798134839488919</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.134406264295895</v>
       </c>
       <c r="E30">
-        <v>-24.18810784741557</v>
+        <v>-24.17273367815952</v>
       </c>
       <c r="F30">
-        <v>-3.278092671774172</v>
+        <v>-2.750946164389456</v>
       </c>
       <c r="G30">
-        <v>3.254298219890636</v>
+        <v>3.872684952807719</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.191787346824364</v>
       </c>
       <c r="E31">
-        <v>-24.81898314684615</v>
+        <v>-25.1139090735437</v>
       </c>
       <c r="F31">
-        <v>-3.037432888810651</v>
+        <v>-2.803544180997613</v>
       </c>
       <c r="G31">
-        <v>3.004375205494436</v>
+        <v>3.088469683283003</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.277621444543058</v>
       </c>
       <c r="E32">
-        <v>-24.63213378081566</v>
+        <v>-24.16936449349782</v>
       </c>
       <c r="F32">
-        <v>-3.295518208459462</v>
+        <v>-2.974161358217422</v>
       </c>
       <c r="G32">
-        <v>4.569495199004597</v>
+        <v>2.749142076053245</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.396785070609818</v>
       </c>
       <c r="E33">
-        <v>-21.67944193054237</v>
+        <v>-24.67190736802503</v>
       </c>
       <c r="F33">
-        <v>-2.813516067792514</v>
+        <v>-3.195369417828405</v>
       </c>
       <c r="G33">
-        <v>3.702125646624467</v>
+        <v>2.464163694941703</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.556376811715824</v>
       </c>
       <c r="E34">
-        <v>-23.74764582305951</v>
+        <v>-24.30314920110643</v>
       </c>
       <c r="F34">
-        <v>-3.891034019434235</v>
+        <v>-3.170963229039723</v>
       </c>
       <c r="G34">
-        <v>3.775043722672454</v>
+        <v>2.908756718683666</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.743884787707358</v>
       </c>
       <c r="E35">
-        <v>-21.41785010101529</v>
+        <v>-23.20124920624202</v>
       </c>
       <c r="F35">
-        <v>-3.028109613692143</v>
+        <v>-3.082819967177439</v>
       </c>
       <c r="G35">
-        <v>3.924167246488925</v>
+        <v>2.552409596836516</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.9607391792145</v>
       </c>
       <c r="E36">
-        <v>-20.99324679263409</v>
+        <v>-22.90637762123256</v>
       </c>
       <c r="F36">
-        <v>-2.818764603656652</v>
+        <v>-3.070083818359396</v>
       </c>
       <c r="G36">
-        <v>2.749807495706639</v>
+        <v>2.157554209276562</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.202993474953461</v>
       </c>
       <c r="E37">
-        <v>-21.7218465611502</v>
+        <v>-22.46242414341659</v>
       </c>
       <c r="F37">
-        <v>-3.094787391045683</v>
+        <v>-3.032244823766918</v>
       </c>
       <c r="G37">
-        <v>2.771792828632939</v>
+        <v>1.905694525739889</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.451338229460189</v>
       </c>
       <c r="E38">
-        <v>-20.92728956871237</v>
+        <v>-20.1626386186212</v>
       </c>
       <c r="F38">
-        <v>-2.869560092796317</v>
+        <v>-3.093481884018871</v>
       </c>
       <c r="G38">
-        <v>3.761841267061841</v>
+        <v>1.993619304717393</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.707957241275746</v>
       </c>
       <c r="E39">
-        <v>-20.15933736106961</v>
+        <v>-19.33366975219909</v>
       </c>
       <c r="F39">
-        <v>-3.133400080792376</v>
+        <v>-3.045207116885924</v>
       </c>
       <c r="G39">
-        <v>3.23697413508363</v>
+        <v>1.782207866579535</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.966361157598946</v>
       </c>
       <c r="E40">
-        <v>-18.66152646913661</v>
+        <v>-20.1357168406456</v>
       </c>
       <c r="F40">
-        <v>-2.982745729612633</v>
+        <v>-3.105283634406556</v>
       </c>
       <c r="G40">
-        <v>2.314063560191147</v>
+        <v>0.6529840936796721</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.21274711746625</v>
       </c>
       <c r="E41">
-        <v>-18.36211735317147</v>
+        <v>-19.27755290229604</v>
       </c>
       <c r="F41">
-        <v>-2.807502948815592</v>
+        <v>-2.80766199535693</v>
       </c>
       <c r="G41">
-        <v>2.270910599086748</v>
+        <v>0.2604791934526016</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.45593329137637</v>
       </c>
       <c r="E42">
-        <v>-16.81914398995997</v>
+        <v>-17.95992093418023</v>
       </c>
       <c r="F42">
-        <v>-3.230850050425113</v>
+        <v>-3.282308233487019</v>
       </c>
       <c r="G42">
-        <v>2.247107776659388</v>
+        <v>1.205769056190557</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.690459255334574</v>
       </c>
       <c r="E43">
-        <v>-17.04271928019266</v>
+        <v>-16.29701093687558</v>
       </c>
       <c r="F43">
-        <v>-2.579276960568092</v>
+        <v>-2.971675427641621</v>
       </c>
       <c r="G43">
-        <v>1.15247258355383</v>
+        <v>0.6796902645449727</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.910796727540564</v>
       </c>
       <c r="E44">
-        <v>-15.63818136739565</v>
+        <v>-16.60722499182302</v>
       </c>
       <c r="F44">
-        <v>-2.695157276545715</v>
+        <v>-2.710434028188143</v>
       </c>
       <c r="G44">
-        <v>0.7549455857436854</v>
+        <v>-0.7418050212894466</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.127997054534839</v>
       </c>
       <c r="E45">
-        <v>-14.50104984475157</v>
+        <v>-14.90688262837097</v>
       </c>
       <c r="F45">
-        <v>-2.805846214009993</v>
+        <v>-2.551310448682178</v>
       </c>
       <c r="G45">
-        <v>1.415356383736277</v>
+        <v>-0.5987100008999888</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.335043102115545</v>
       </c>
       <c r="E46">
-        <v>-14.17467819454476</v>
+        <v>-13.74764762409545</v>
       </c>
       <c r="F46">
-        <v>-2.975358349114467</v>
+        <v>-2.610231393675904</v>
       </c>
       <c r="G46">
-        <v>0.242294366805385</v>
+        <v>-0.1880268951167803</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.534089013184618</v>
       </c>
       <c r="E47">
-        <v>-12.85605449062126</v>
+        <v>-13.47286434978402</v>
       </c>
       <c r="F47">
-        <v>-2.495059331827675</v>
+        <v>-2.695238456551189</v>
       </c>
       <c r="G47">
-        <v>-0.7575863918751523</v>
+        <v>-1.273859347633415</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.735173554980507</v>
       </c>
       <c r="E48">
-        <v>-10.72100579327691</v>
+        <v>-13.18805503401961</v>
       </c>
       <c r="F48">
-        <v>-2.553192499421338</v>
+        <v>-2.640580290212269</v>
       </c>
       <c r="G48">
-        <v>0.3728126246911516</v>
+        <v>-1.478596725964103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.927744384405178</v>
       </c>
       <c r="E49">
-        <v>-10.23271855492584</v>
+        <v>-12.39158702555055</v>
       </c>
       <c r="F49">
-        <v>-2.244371333085863</v>
+        <v>-2.131396929957261</v>
       </c>
       <c r="G49">
-        <v>-0.1570633626879769</v>
+        <v>-0.9170123334098349</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.12023429099796</v>
       </c>
       <c r="E50">
-        <v>-10.46814939011061</v>
+        <v>-11.74267028567341</v>
       </c>
       <c r="F50">
-        <v>-2.575508717252757</v>
+        <v>-2.870525140820579</v>
       </c>
       <c r="G50">
-        <v>0.4639618750239051</v>
+        <v>-1.43958856787487</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.31792702048619</v>
       </c>
       <c r="E51">
-        <v>-8.303620326976322</v>
+        <v>-9.839665124956085</v>
       </c>
       <c r="F51">
-        <v>-2.40345100911948</v>
+        <v>-2.31453073863337</v>
       </c>
       <c r="G51">
-        <v>-1.682506467909972</v>
+        <v>-2.413517960073061</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.50610558969792</v>
       </c>
       <c r="E52">
-        <v>-10.61658371113403</v>
+        <v>-9.250152907111564</v>
       </c>
       <c r="F52">
-        <v>-2.014592155958114</v>
+        <v>-2.038584989412799</v>
       </c>
       <c r="G52">
-        <v>-2.211501850175654</v>
+        <v>-2.528754739749552</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.69562030742853</v>
       </c>
       <c r="E53">
-        <v>-8.467619013164104</v>
+        <v>-9.302280171413859</v>
       </c>
       <c r="F53">
-        <v>-2.29207784018049</v>
+        <v>-2.508579944576168</v>
       </c>
       <c r="G53">
-        <v>-1.496417392601999</v>
+        <v>-3.166028134968176</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.8840089867088</v>
       </c>
       <c r="E54">
-        <v>-7.354103482470025</v>
+        <v>-8.872786111104379</v>
       </c>
       <c r="F54">
-        <v>-2.339119168250668</v>
+        <v>-2.41698239064421</v>
       </c>
       <c r="G54">
-        <v>-2.06916163416915</v>
+        <v>-4.155384669379371</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.05505271456315</v>
       </c>
       <c r="E55">
-        <v>-5.46433957975113</v>
+        <v>-8.994303182626204</v>
       </c>
       <c r="F55">
-        <v>-2.114427823710913</v>
+        <v>-2.079744908923101</v>
       </c>
       <c r="G55">
-        <v>-2.10128054699116</v>
+        <v>-3.095735321532831</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.21866142116316</v>
       </c>
       <c r="E56">
-        <v>-6.284016017509503</v>
+        <v>-7.767553159370328</v>
       </c>
       <c r="F56">
-        <v>-2.614954744606667</v>
+        <v>-2.42113085459743</v>
       </c>
       <c r="G56">
-        <v>-2.645256147822044</v>
+        <v>-3.695235392148372</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.36548825790207</v>
       </c>
       <c r="E57">
-        <v>-4.545000486031949</v>
+        <v>-7.461247177491505</v>
       </c>
       <c r="F57">
-        <v>-2.715764572425158</v>
+        <v>-2.227390629695876</v>
       </c>
       <c r="G57">
-        <v>-2.782855662616312</v>
+        <v>-3.736415268111366</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.48277289024078</v>
       </c>
       <c r="E58">
-        <v>-5.554691693152169</v>
+        <v>-5.527289896931756</v>
       </c>
       <c r="F58">
-        <v>-2.498683439214922</v>
+        <v>-2.279958825077533</v>
       </c>
       <c r="G58">
-        <v>-3.823360125609246</v>
+        <v>-4.03369894699238</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.5778750725376</v>
       </c>
       <c r="E59">
-        <v>-3.873228537838097</v>
+        <v>-6.711707745163931</v>
       </c>
       <c r="F59">
-        <v>-2.114236470840866</v>
+        <v>-2.682176759343847</v>
       </c>
       <c r="G59">
-        <v>-2.905971540676268</v>
+        <v>-4.697529538527038</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.63652555992473</v>
       </c>
       <c r="E60">
-        <v>-3.044644591706636</v>
+        <v>-5.806787312685171</v>
       </c>
       <c r="F60">
-        <v>-2.706737024469449</v>
+        <v>-2.333904595450045</v>
       </c>
       <c r="G60">
-        <v>-2.729691611801155</v>
+        <v>-4.372943790583656</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.65352258874339</v>
       </c>
       <c r="E61">
-        <v>-5.37784119773062</v>
+        <v>-5.484047498632513</v>
       </c>
       <c r="F61">
-        <v>-2.3948757497657</v>
+        <v>-2.373833560999786</v>
       </c>
       <c r="G61">
-        <v>-2.898065957928488</v>
+        <v>-4.488511624814073</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.63451770576931</v>
       </c>
       <c r="E62">
-        <v>-1.705411802574236</v>
+        <v>-5.003490365412541</v>
       </c>
       <c r="F62">
-        <v>-2.809332812408376</v>
+        <v>-2.265682741257686</v>
       </c>
       <c r="G62">
-        <v>-3.681986588900209</v>
+        <v>-4.112033075542614</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.56483683724732</v>
       </c>
       <c r="E63">
-        <v>-4.162679539460371</v>
+        <v>-4.840927205485191</v>
       </c>
       <c r="F63">
-        <v>-3.049395342474479</v>
+        <v>-2.186337569580535</v>
       </c>
       <c r="G63">
-        <v>-4.221575716891559</v>
+        <v>-4.24782834301798</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.44775028855151</v>
       </c>
       <c r="E64">
-        <v>-2.946517088434427</v>
+        <v>-3.819982740455909</v>
       </c>
       <c r="F64">
-        <v>-2.613233397143649</v>
+        <v>-2.55160120564056</v>
       </c>
       <c r="G64">
-        <v>-4.02970311852648</v>
+        <v>-4.584123490533765</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.28524688164043</v>
       </c>
       <c r="E65">
-        <v>-2.455680319217045</v>
+        <v>-4.006252461813414</v>
       </c>
       <c r="F65">
-        <v>-2.812998338165764</v>
+        <v>-2.331079862606499</v>
       </c>
       <c r="G65">
-        <v>-4.433665816864967</v>
+        <v>-4.962350007849959</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.06270035922739</v>
       </c>
       <c r="E66">
-        <v>-1.693483802038032</v>
+        <v>-4.031145483433578</v>
       </c>
       <c r="F66">
-        <v>-2.806971965310398</v>
+        <v>-2.281287526391623</v>
       </c>
       <c r="G66">
-        <v>-3.605340838575002</v>
+        <v>-4.164448943065896</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.78946170147841</v>
       </c>
       <c r="E67">
-        <v>-1.931595493835347</v>
+        <v>-3.979828815978657</v>
       </c>
       <c r="F67">
-        <v>-2.894524601214486</v>
+        <v>-2.768128161058323</v>
       </c>
       <c r="G67">
-        <v>-2.62896495322329</v>
+        <v>-4.20190445529721</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.46590639514745</v>
       </c>
       <c r="E68">
-        <v>-1.16722983760666</v>
+        <v>-4.043802568285017</v>
       </c>
       <c r="F68">
-        <v>-2.986537167215246</v>
+        <v>-2.453653387198741</v>
       </c>
       <c r="G68">
-        <v>-2.157851149166226</v>
+        <v>-3.68797867632629</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.08259761456042</v>
       </c>
       <c r="E69">
-        <v>-1.091572622360511</v>
+        <v>-3.786186738936665</v>
       </c>
       <c r="F69">
-        <v>-2.899937153824378</v>
+        <v>-2.404514632864675</v>
       </c>
       <c r="G69">
-        <v>-3.397365746706908</v>
+        <v>-4.360479586628299</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.654800005346278</v>
       </c>
       <c r="E70">
-        <v>-2.547957034071344</v>
+        <v>-2.992630539254534</v>
       </c>
       <c r="F70">
-        <v>-2.854095301753453</v>
+        <v>-2.552330168955024</v>
       </c>
       <c r="G70">
-        <v>-3.596422228892206</v>
+        <v>-4.147244037898303</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.184214904102685</v>
       </c>
       <c r="E71">
-        <v>-2.528760832752829</v>
+        <v>-3.077743208228699</v>
       </c>
       <c r="F71">
-        <v>-2.781446652160534</v>
+        <v>-2.737239997342735</v>
       </c>
       <c r="G71">
-        <v>-2.490008114757922</v>
+        <v>-3.408479248082241</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.670265546569489</v>
       </c>
       <c r="E72">
-        <v>-2.554097644825745</v>
+        <v>-3.885817695579421</v>
       </c>
       <c r="F72">
-        <v>-2.808781948085515</v>
+        <v>-2.569082242941839</v>
       </c>
       <c r="G72">
-        <v>-2.063417837658515</v>
+        <v>-3.382110752861946</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.131226205898313</v>
       </c>
       <c r="E73">
-        <v>-3.611147633118183</v>
+        <v>-3.945584495532654</v>
       </c>
       <c r="F73">
-        <v>-3.403484302270738</v>
+        <v>-2.625633228796155</v>
       </c>
       <c r="G73">
-        <v>-1.953388546115298</v>
+        <v>-2.995521797513554</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.568540197157091</v>
       </c>
       <c r="E74">
-        <v>-1.904528804691501</v>
+        <v>-4.145951356476036</v>
       </c>
       <c r="F74">
-        <v>-3.264307809824185</v>
+        <v>-2.598644190445544</v>
       </c>
       <c r="G74">
-        <v>-2.295808202878734</v>
+        <v>-2.450162388647254</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.988596044769946</v>
       </c>
       <c r="E75">
-        <v>-4.288204310478986</v>
+        <v>-4.329245870410502</v>
       </c>
       <c r="F75">
-        <v>-3.535233652583791</v>
+        <v>-2.169074392906194</v>
       </c>
       <c r="G75">
-        <v>-1.808356856585366</v>
+        <v>-2.199127030949859</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.405442634118315</v>
       </c>
       <c r="E76">
-        <v>-2.376545235933006</v>
+        <v>-5.789660623988162</v>
       </c>
       <c r="F76">
-        <v>-3.197353357758109</v>
+        <v>-2.460654748487203</v>
       </c>
       <c r="G76">
-        <v>-0.6094229262650703</v>
+        <v>-1.897655511961667</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.818522415041656</v>
       </c>
       <c r="E77">
-        <v>-5.033690758569695</v>
+        <v>-4.8438842990122</v>
       </c>
       <c r="F77">
-        <v>-3.184637918125137</v>
+        <v>-2.824151476877057</v>
       </c>
       <c r="G77">
-        <v>-1.303836337491516</v>
+        <v>-1.728092679985737</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.237925826603876</v>
       </c>
       <c r="E78">
-        <v>-4.790715485688142</v>
+        <v>-7.008947722079398</v>
       </c>
       <c r="F78">
-        <v>-3.528664699079592</v>
+        <v>-3.17218755606106</v>
       </c>
       <c r="G78">
-        <v>-0.08789282419044465</v>
+        <v>-1.12575878238858</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.67465962213254</v>
       </c>
       <c r="E79">
-        <v>-5.268510249763434</v>
+        <v>-6.345562507747752</v>
       </c>
       <c r="F79">
-        <v>-3.383489169901964</v>
+        <v>-3.237050380435067</v>
       </c>
       <c r="G79">
-        <v>0.6798690340040934</v>
+        <v>-1.299234679191929</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.129482370421045</v>
       </c>
       <c r="E80">
-        <v>-4.878318815366526</v>
+        <v>-6.730845076320346</v>
       </c>
       <c r="F80">
-        <v>-3.614968156940258</v>
+        <v>-2.803805945096898</v>
       </c>
       <c r="G80">
-        <v>1.765158557052288</v>
+        <v>-0.2997611176127221</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.619218320348783</v>
       </c>
       <c r="E81">
-        <v>-6.635226347648386</v>
+        <v>-7.254132890276694</v>
       </c>
       <c r="F81">
-        <v>-4.015277532710522</v>
+        <v>-3.09591397071349</v>
       </c>
       <c r="G81">
-        <v>1.567201175986028</v>
+        <v>-0.1960582785950521</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.156430441583246</v>
       </c>
       <c r="E82">
-        <v>-7.05073648022218</v>
+        <v>-9.27273187851381</v>
       </c>
       <c r="F82">
-        <v>-3.736418415334305</v>
+        <v>-2.665437110868074</v>
       </c>
       <c r="G82">
-        <v>1.248739937290297</v>
+        <v>0.6245299547696362</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.746068510330049</v>
       </c>
       <c r="E83">
-        <v>-9.383525523585472</v>
+        <v>-9.582126279665864</v>
       </c>
       <c r="F83">
-        <v>-3.928673377482639</v>
+        <v>-3.382722101686972</v>
       </c>
       <c r="G83">
-        <v>2.782227668172721</v>
+        <v>1.583482438948164</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.409548337548957</v>
       </c>
       <c r="E84">
-        <v>-9.831396131418078</v>
+        <v>-11.18903716739166</v>
       </c>
       <c r="F84">
-        <v>-3.617107001574286</v>
+        <v>-3.469631924486487</v>
       </c>
       <c r="G84">
-        <v>1.656231677173648</v>
+        <v>1.208649230809723</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.157187585798179</v>
       </c>
       <c r="E85">
-        <v>-11.35753262826906</v>
+        <v>-11.43406836747269</v>
       </c>
       <c r="F85">
-        <v>-3.988845157254592</v>
+        <v>-3.450480898501166</v>
       </c>
       <c r="G85">
-        <v>3.069198997698905</v>
+        <v>1.901576207089036</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.993923622934886</v>
       </c>
       <c r="E86">
-        <v>-13.51840721287916</v>
+        <v>-12.52784880844135</v>
       </c>
       <c r="F86">
-        <v>-4.279026400292273</v>
+        <v>-3.648323198781383</v>
       </c>
       <c r="G86">
-        <v>1.3360324020698</v>
+        <v>2.421288819662602</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.937049050832498</v>
       </c>
       <c r="E87">
-        <v>-14.02673294871417</v>
+        <v>-13.88720160758983</v>
       </c>
       <c r="F87">
-        <v>-3.911557650205995</v>
+        <v>-3.673534560685586</v>
       </c>
       <c r="G87">
-        <v>3.578761477649065</v>
+        <v>2.203934952281752</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.987672882523767</v>
       </c>
       <c r="E88">
-        <v>-14.22773379601862</v>
+        <v>-15.60170903773787</v>
       </c>
       <c r="F88">
-        <v>-4.210228830754969</v>
+        <v>-3.569754207360655</v>
       </c>
       <c r="G88">
-        <v>2.764920136093412</v>
+        <v>2.750873491370284</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.147684029100368</v>
       </c>
       <c r="E89">
-        <v>-17.11351291435457</v>
+        <v>-16.65658535850663</v>
       </c>
       <c r="F89">
-        <v>-4.564960603655801</v>
+        <v>-3.946684569921709</v>
       </c>
       <c r="G89">
-        <v>3.432647239727793</v>
+        <v>2.240221841937704</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.424981859297907</v>
       </c>
       <c r="E90">
-        <v>-17.48529157343629</v>
+        <v>-16.8548781783545</v>
       </c>
       <c r="F90">
-        <v>-4.565079060194401</v>
+        <v>-3.698618354009758</v>
       </c>
       <c r="G90">
-        <v>2.888049256335525</v>
+        <v>2.303668447197836</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.809260968829947</v>
       </c>
       <c r="E91">
-        <v>-20.30163107133863</v>
+        <v>-20.19258541723392</v>
       </c>
       <c r="F91">
-        <v>-4.570675510367715</v>
+        <v>-4.056227875267916</v>
       </c>
       <c r="G91">
-        <v>4.104598599470283</v>
+        <v>2.528384967858025</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.297837796993563</v>
       </c>
       <c r="E92">
-        <v>-20.96614387569818</v>
+        <v>-21.92134848355812</v>
       </c>
       <c r="F92">
-        <v>-4.133592420484972</v>
+        <v>-3.7058508298036</v>
       </c>
       <c r="G92">
-        <v>2.648372380383369</v>
+        <v>2.08257366335761</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.886931466180908</v>
       </c>
       <c r="E93">
-        <v>-22.9592384983241</v>
+        <v>-24.04940974550864</v>
       </c>
       <c r="F93">
-        <v>-4.182339357037515</v>
+        <v>-3.69357690999632</v>
       </c>
       <c r="G93">
-        <v>1.782840180777536</v>
+        <v>2.409010006257445</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.553883752657498</v>
       </c>
       <c r="E94">
-        <v>-25.83226543385445</v>
+        <v>-26.16334216855523</v>
       </c>
       <c r="F94">
-        <v>-3.943410861945845</v>
+        <v>-3.911472328363507</v>
       </c>
       <c r="G94">
-        <v>0.9057177612387131</v>
+        <v>1.854063257509416</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.291535929499997</v>
       </c>
       <c r="E95">
-        <v>-27.22883323239796</v>
+        <v>-27.79307656527968</v>
       </c>
       <c r="F95">
-        <v>-4.37472188776588</v>
+        <v>-4.226154194073789</v>
       </c>
       <c r="G95">
-        <v>1.340461912001345</v>
+        <v>1.380850567580453</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.091095724678561</v>
       </c>
       <c r="E96">
-        <v>-30.25095791039386</v>
+        <v>-29.44437102675466</v>
       </c>
       <c r="F96">
-        <v>-5.111883554414952</v>
+        <v>-4.257231225557216</v>
       </c>
       <c r="G96">
-        <v>0.5663603590991022</v>
+        <v>1.420107016585131</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.918638407279336</v>
       </c>
       <c r="E97">
-        <v>-31.19917734709696</v>
+        <v>-32.52000188938818</v>
       </c>
       <c r="F97">
-        <v>-4.811330323126819</v>
+        <v>-4.359744176755862</v>
       </c>
       <c r="G97">
-        <v>-0.2109060753386834</v>
+        <v>1.140213633421909</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.781887474033365</v>
       </c>
       <c r="E98">
-        <v>-35.4158025207031</v>
+        <v>-34.96821041402197</v>
       </c>
       <c r="F98">
-        <v>-4.429624422488626</v>
+        <v>-4.4283147736248</v>
       </c>
       <c r="G98">
-        <v>0.2174950701707045</v>
+        <v>-0.2397641008045104</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.636804095546323</v>
       </c>
       <c r="E99">
-        <v>-36.22565669833884</v>
+        <v>-36.36279700518713</v>
       </c>
       <c r="F99">
-        <v>-5.26302747072975</v>
+        <v>-4.422594896708469</v>
       </c>
       <c r="G99">
-        <v>-0.07580602242656556</v>
+        <v>0.3616461545871898</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.498993533670118</v>
       </c>
       <c r="E100">
-        <v>-39.12684394948589</v>
+        <v>-38.85537098967406</v>
       </c>
       <c r="F100">
-        <v>-5.002467817648776</v>
+        <v>-4.477156972428665</v>
       </c>
       <c r="G100">
-        <v>-1.1138573711749</v>
+        <v>-1.061779179296625</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.29724997915726</v>
       </c>
       <c r="E101">
-        <v>-42.81740309033198</v>
+        <v>-40.54620582194701</v>
       </c>
       <c r="F101">
-        <v>-4.905120565573987</v>
+        <v>-4.584129853723984</v>
       </c>
       <c r="G101">
-        <v>-1.117833336367564</v>
+        <v>-0.6732105177157476</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.11745329598219</v>
       </c>
       <c r="E102">
-        <v>-44.00699019164392</v>
+        <v>-43.5480180297815</v>
       </c>
       <c r="F102">
-        <v>-5.472215919326112</v>
+        <v>-4.88251193404938</v>
       </c>
       <c r="G102">
-        <v>-1.823141752963751</v>
+        <v>-1.169974428611086</v>
       </c>
     </row>
   </sheetData>
